--- a/Hand_edited_log/1/student/AnhDThe187386/TC2/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/AnhDThe187386/TC2/GradeDetail.xlsx
@@ -152,10 +152,7 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
+    <x:t>PASS</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -168,6 +165,30 @@
   </x:si>
   <x:si>
     <x:t>Connection established</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"StudentId":"S123","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -194,7 +215,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -203,7 +224,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -226,7 +252,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -236,8 +262,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -247,6 +276,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -873,11 +906,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P4"/>
+  <x:dimension ref="A1:P12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -886,11 +919,11 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="108.853482" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="14.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -976,22 +1009,22 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P2" s="2" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P2" s="2" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
@@ -1011,10 +1044,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1026,22 +1059,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="2" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="2" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
@@ -1061,10 +1094,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1076,22 +1109,422 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P4" s="2" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P4" s="2" t="s">
-        <x:v>45</x:v>
+    </x:row>
+    <x:row r="5" spans="1:16">
+      <x:c r="A5" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:16">
+      <x:c r="A6" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:16">
+      <x:c r="A7" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P7" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:16">
+      <x:c r="A8" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:16">
+      <x:c r="A9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:16">
+      <x:c r="A10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/AnhDThe187386/TC2/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/AnhDThe187386/TC2/GradeDetail.xlsx
@@ -134,6 +134,12 @@
     <x:t>ActualData</x:t>
   </x:si>
   <x:si>
+    <x:t>ActualSourcePort</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActualDestPort</x:t>
+  </x:si>
+  <x:si>
     <x:t>NetworkResult</x:t>
   </x:si>
   <x:si>
@@ -167,13 +173,16 @@
     <x:t>Connection established</x:t>
   </x:si>
   <x:si>
+    <x:t>Connection acknowledged (ACK)</x:t>
+  </x:si>
+  <x:si>
     <x:t>(Not validated by this test case)</x:t>
   </x:si>
   <x:si>
     <x:t>PSH, ACK</x:t>
   </x:si>
   <x:si>
-    <x:t>Data transfer in progress</x:t>
+    <x:t>Client sending data</x:t>
   </x:si>
   <x:si>
     <x:t>S123</x:t>
@@ -182,13 +191,19 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>Server sending data</x:t>
+  </x:si>
+  <x:si>
     <x:t>{"StudentId":"S123","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
   </x:si>
   <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
+    <x:t>Server closing connection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client closing connection</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -906,7 +921,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:R12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -924,10 +939,12 @@
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="108.853482" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14.424911" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:16" s="1" customFormat="1">
+    <x:row r="1" spans="1:18" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -976,8 +993,14 @@
       <x:c r="P1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:16">
+      <x:c r="Q1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R1" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:18">
       <x:c r="A2" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -985,7 +1008,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -994,40 +1017,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:16">
+      <x:c r="P2" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R2" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:18">
       <x:c r="A3" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1035,7 +1064,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1044,40 +1073,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q3" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:16">
+    </x:row>
+    <x:row r="4" spans="1:18">
       <x:c r="A4" s="0">
         <x:v>3</x:v>
       </x:c>
@@ -1085,7 +1120,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1094,45 +1129,51 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:16">
+      <x:c r="P4" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="Q4" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R4" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:18">
       <x:c r="A5" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>17</x:v>
@@ -1159,80 +1200,92 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="P5" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:16">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="P5" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="Q5" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R5" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:18">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:16">
+      <x:c r="P6" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:18">
       <x:c r="A7" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>17</x:v>
@@ -1259,80 +1312,92 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:16">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P7" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q7" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="R7" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:18">
       <x:c r="A8" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
+      <x:c r="P8" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="Q8" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:18">
       <x:c r="A9" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1359,80 +1424,92 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q9" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
+    </x:row>
+    <x:row r="10" spans="1:18">
       <x:c r="A10" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
+      <x:c r="P10" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:18">
       <x:c r="A11" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1459,72 +1536,84 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
+    </x:row>
+    <x:row r="12" spans="1:18">
       <x:c r="A12" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="3" t="s">
-        <x:v>53</x:v>
+      <x:c r="P12" s="0">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>55745</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/AnhDThe187386/TC2/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/AnhDThe187386/TC2/GradeDetail.xlsx
@@ -1047,10 +1047,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1103,10 +1103,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1159,10 +1159,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1215,10 +1215,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>56</x:v>
@@ -1271,10 +1271,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1327,10 +1327,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>56</x:v>
@@ -1383,10 +1383,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1439,10 +1439,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1495,10 +1495,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>56</x:v>
@@ -1551,10 +1551,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>56</x:v>
@@ -1607,10 +1607,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>4003</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>55745</x:v>
+        <x:v>51700</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>56</x:v>
